--- a/borchestra_items.xlsx
+++ b/borchestra_items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,1323 +441,682 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CarnivorousPolyp_TW</t>
+          <t>GF_Chalcanthite_OS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carnivorous Polyp</t>
+          <t>Chalcanthite</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All enemies are inflicted with 6 Coral Colony on combat start.</t>
+          <t>Upon lucky pigment being generated, apply triple the lucky pigment generated as Shield to this party member's slot.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marine fauna miracle.\</t>
+          <t>\!Vitriolic blues.\!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GreatSinking_TW</t>
+          <t>GF_Golden_Pickaxe_EW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Great Sinking</t>
+          <t>Golden Pickaxe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deal 5 indirect damage to All enemies and apply 5 Shield to All party members upon this party member receiving overflow damage.</t>
+          <t>When this party member deals damage, 30% chance to gain 3 coins. 15% chance to consume this item when this effect triggers.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>We're all in the same boat.\</t>
+          <t>\!Gold digging for dummies.\!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weightless_TW</t>
+          <t>GF_Candy_Stones_MA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Weightless</t>
+          <t>Candy Stones</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remove 1 ability from opposing enemy upon dealing damage. This item activates only if no other party members are holding an item.</t>
+          <t>At the end of the turn, heal this party member 1 health and apply 2 Shield to their slot.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nothing excess.\</t>
+          <t>\!Better than gelt!\!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yesterday'sSmile_TW</t>
+          <t>GF_Irish_Car_Bomb_OS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yesterday's Smile</t>
+          <t>Irish Car Bomb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inflict Cursed to this party member on combat start. 
-At the end of the combat, remove Cursed from this party member and heal them 1-25 health.</t>
+          <t>Adds 'Drink Under' as an extra ability, a potent but dangerous damaging move that hits everyone.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Decorate your new face.\</t>
+          <t>\!What happens in...\!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AppleStructure_TW</t>
+          <t>GF_Off_Brandy_EW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apple Structure</t>
+          <t>Off-Brandy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>At the end of the fourth turn deal 15 damage to All enemies.</t>
+          <t>Adds Tainted and Leaky to this party member as additional passives.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Witajcie w naszym poradniku!\</t>
+          <t>\!Poor man's poison.\!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BrainjuiceStrider_TW</t>
+          <t>GF_Whiskey_Stone_MA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brainjuice Strider</t>
+          <t>Whiskey Stones</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Whenever enemy dies, inflict 4 Infirm to All enemies.</t>
+          <t>This party member now has Grey health, along with the Inanimate and Swift Passives.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>It twitches and squirts. Such a funny thing.\</t>
+          <t>\!Whiskey, soured.\!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FingerGun_SW</t>
+          <t>GF_Sergal_Spear_OS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finger Gun</t>
+          <t>Sergal Spear</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15% chance to refresh this party member's abilities upon using an ability. 
-Starting from a second ability used by this party member in a single turn, deal 5 indirect damage to All enemies upon using an ability.</t>
+          <t>This party member does 2 additional damage with abilities, but exhausts their movement after using an ability.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BANG BANG BANG BANG BANG\</t>
+          <t>\!Requires two hands to wield.\!</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Genie_TW</t>
+          <t>GF_Nap_Sack_OS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Genie</t>
+          <t>Nap Sack</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Upon dealing damage, increase Charges Value by 1. 
-Adds \</t>
+          <t>This unit is Exhausted at the start of the first turn. Apply 2 Well-Rested to this party member at the start of the first turn.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The purgatory needs a cleansing but it cannot cleanse itself by its own will alone.\</t>
+          <t>\!Get in the bag!\!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Balloon_TW</t>
+          <t>GF_Plastic_Bag_HV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Balloon</t>
+          <t>Plastic Bag</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Upon ending a turn at full health, deal 5 indirect damage to Opposing enemy and increase this party member's maximum health by 3. The damage of this item is increased by 1 per 5 health this party member has.</t>
+          <t>When this party member is manually swapped to a slot, 1 Constricted is applied to the Opposing slot.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No limit to perfection.\</t>
+          <t>\!Do you ever feel...\!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NotToughSkin_TW</t>
+          <t>GF_Crab_Claw_OS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Not Tough Skin</t>
+          <t>Crab Claw</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Produce an gross fleshy item at the end of the combat.
-Upon taking direct damage, there is a 30% chance to produce 3 gross fleshy items and destroy this item.</t>
+          <t>This party member has Constricting and Dominance as additional passives.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ouch! Ow! Oi! Ahh! Ouchy!\</t>
+          <t>\!What happens in...\!</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MeltedCore_TW</t>
+          <t>GF_Inscissors_HV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Melted Core</t>
+          <t>Inscissors</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Whenever enemy dies, increase \</t>
+          <t>When this party member uses an ability, deal 1 damage to them and then heal them 2 health.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Everything hurts.\</t>
+          <t>\!Cut your teeth on it.\!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CowTool_TW</t>
+          <t>GF_Neural_Worm_EW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cow Tool</t>
+          <t>Neural Worm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>On combat start, add an additional ability to the Opposing enemy, which does not help them at all.</t>
+          <t>This party member has a 40% chance to be Exhausted on turn start, and a 60% chance to perform a random ability.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lack something in sophistication.\</t>
+          <t>\!Weak to fluoride.\!</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Leftovers1_EW</t>
+          <t>GF_Embalming_Fluid_MA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leftovers</t>
+          <t>Embalming Fluid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Heal this party member 1-5 health at the end of each turn. 
-This item is destroyed at the end of combat.</t>
+          <t>The Left and Right party members gain Immortal and are inflicted with 2 Scars at the start of combat.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>...\</t>
+          <t>\!Comfy company, a human quilt…\!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Leftovers2_EW</t>
+          <t>GF_Naked_Knight_OS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Leftovers</t>
+          <t>Little Knight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Heal this party member 1-5 health at the end of each turn. 
-This item is destroyed at the end of combat.</t>
+          <t>When this party member uses an ability, a coinflip occurs. There is a 50% chance to apply 5 Shield to their position, and a 50% chance to deal 5 Damage to the Opposing enemy.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>...\</t>
+          <t>\!He's pulling his sword out!\!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Leftovers3_EW</t>
+          <t>GF_TowerShield_HV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leftovers</t>
+          <t>Tower Shield</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Heal this party member 1-5 health at the end of each turn. 
-This item is destroyed at the end of combat.</t>
+          <t>When this party member uses an ability, apply 3 Shield to the Left and Right allies.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>...\</t>
+          <t>\!Tower defense.\!</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RareShinyLeftovers_EW</t>
+          <t>GF_Love_Letter_OS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rare Shiny Leftovers</t>
+          <t>Love Letter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Heal this party member 1-5 health at the end of each turn. 
-At the end of combat produce 5 coins and destroy this item.</t>
+          <t>At the start of combat, applies Gaze to the Opposing enemy. This party member deals 4 extra damage to Gazed enemies.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>..!\</t>
+          <t>\!Exodus 20:17\!</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WeirdBluishLeftovers_EW</t>
+          <t>GF_GlassEye_HV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Weird Bluish Leftovers</t>
+          <t>Second Glass Eye</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Heal this party member 1 health at the end of each turn. 
-At the end of combat heal this party member 8 health and destroy this item.</t>
+          <t>When using an ability, there is a 20% chance to cancel one of the Opposing enemy's abilities.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>..?\</t>
+          <t>\!It gazes... intently.\!</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PulsatingWormyLeftovers_EW</t>
+          <t>GF_Blessed_Goblet_EW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pulsating Wormy Leftovers</t>
+          <t>Glistening Goblet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Heal this party member 1-10 health at the end of each turn. 
-At the end of combat deal 4 damage to this party member and destroy this item.</t>
+          <t>When using an ability, this party member heals for the current amount of overflow.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>...hii\</t>
+          <t>\!Humbly, a toast.\!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ClownHorn_SW</t>
+          <t>GF_Apache_Tears_MA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Clown Horn</t>
+          <t>Apache Tears</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Make other party members perform one of their abilities at random on combat start.</t>
+          <t>At the start of the turn, applies 5 Divine Protection to a random party member that doesn't have any. If all party members have Divine Protection, instead heal all party members 6 health and cleanse them of all status effects.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stop it! It's not funny!\</t>
+          <t>\!Unearthed by ApacheThunder!\!</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BaptismalSyringe_SW</t>
+          <t>GF_Panic_Button_OS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Baptismal Syringe</t>
+          <t>Panic Button</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Heal this party member 2 health at the end of each turn. 
-This item only starts working after recieving direct damage.</t>
+          <t>Upon taking what would be lethal damage, this party member instead flees with one health. Ineffective on instant kills. Consumed on use.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Instant Holy Injection!\</t>
+          <t>\!EMERGENCY!!!\!</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>InnerMansion_TW</t>
+          <t>GF_StickyNote_HV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inner Mansion</t>
+          <t>Sticky Note</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>This party member will perform 3 of their abilities at random upon recieving direct damage first time per combat.</t>
+          <t>At the start of combat, the Left and Right party members have the costs of all their abilities removed.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Blood boils.\</t>
+          <t>\!//TBD\!</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PileofLimbs_TW</t>
+          <t>GF_Dusty_Keyboard_MA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pile of Limbs</t>
+          <t>Dusty Keyboard</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>This party member now has Convulsive as a passive. 
-Heal this party member 1 health upon receiving wrong pigment damage.</t>
+          <t>Before using an ability, a random status effect that this party member has is reduced by 2.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Still twitching.\</t>
+          <t>\!Still intact?\!</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>InsidiousTrickster_TW</t>
+          <t>GF_Liquid_Hate_OS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Insidious Trickster</t>
+          <t>Liquid Hate</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Upon this party member performing an action, either deal 10 damage to a random enemy or heal 5 health to a random enemy.</t>
+          <t>This party member does 3 additional damage with abilities, but all damage dealt to this party member penetrates Shield.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>If it helps, it's an accident.\</t>
+          <t>\!This flesh, it hates.\!</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bleach_SW</t>
+          <t>GF_Rose_Tinted_Glasses_MA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bleach</t>
+          <t>Rose-Tinted Glasses</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Heal this party member 2-5 health upon receiving wrong pigment damage. 50% chance to also receive 1 Scar.</t>
+          <t>Adds 'Nostalgia' as an extra ability, an ability that performs a random party member's ability.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>There is nothing better to drink...\</t>
+          <t>\!It was better in the before-fore.\!</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DancingWaters_TW</t>
+          <t>GF_Heart_Of_Pyrite_OS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dancing Waters</t>
+          <t>Heart of Pyrite</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Adds \</t>
+          <t>Upon this party member taking damage, gain an equivelent amount of gold and consume this item.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>So beautiful. I'm not gonna drink this though.\</t>
+          <t>\!Willing to trade it for worthless dollars.\!</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reaper'sDuty_TW</t>
+          <t>GF_Amniotic_Fluids_HV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reaper's Duty</t>
+          <t>Amniotic Fluids</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>This party member now has Harvester as a passive. 
-On turn end, reduce this party member's maximum health to their current health value and deal indirect damage to All enemies equal to maximum health removed.</t>
+          <t>When this party member takes damage, the Left or Right party member is healed 5 HP.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The harvest day has come.\</t>
+          <t>\!Stop being a baby!\!</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WormholePiercer_TW</t>
+          <t>GF_ManifestationOfWar_OS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wormhole Piercer</t>
+          <t>Manifestation Of War</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>On combat start, adds \</t>
+          <t>Upon an enemy dying, refresh this party member's abilities.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yeah. I would say it's pretty sharp.\</t>
+          <t>\!Book of Revelations, chapter seven!\!</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WormCycle_TW</t>
+          <t>GF_The_Tick_EW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Worm Cycle</t>
+          <t>The Tick</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Whenever enemy dies, gain 0-3 maximum health and 0-3 Partaking.</t>
+          <t>At the start of combat, this party member's abilities are all changed to only cost Red.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Couldn't be better. Couldn't be worse.\</t>
+          <t>\!No, not that one.\!</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SupremeCarnivorousCreature_EW</t>
+          <t>GF_Adverse_Action_Notice_OS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supreme Carnivorous Creature</t>
+          <t>Adverse Action Notice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Upon dealing damage deal 6 indirect damage to a random enemy 2 times.</t>
+          <t>When this party member takes damage, this item has an 80% chance to negate it, and a 20% chance to multiply it by one to seven.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The jaw of incredible strength, the brain could develop a little more.\</t>
+          <t>\!Begged them for repentance!\!</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SupremeHerbivoreCreature_EW</t>
+          <t>GF_FaustianContract_HV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supreme Herbivore Creature</t>
+          <t>Faustian Contract</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Upon receiving any damage heal 3 health to a random ally 3 times.</t>
+          <t>This party member gains Fatalism as a passive, protecting them from indirect and direct damage completely. After 3 turns, this party member is killed instantly.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Flirtatiousness and Intelligence are off the charts.\</t>
+          <t>\!Stumblin’ on down my side of the road.\!</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SupremeOmnivoreCreature_EW</t>
+          <t>GF_Cement_Shoes_MA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supreme Omnivore Creature</t>
+          <t>Cement Shoes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Upon manually moving gain 4 Shield. 40% chance to also refresh movement</t>
+          <t>Adds Anchored to this party member as an additional passive, but heals them 5 health at the end of every turn.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Jack of all traits, master of none.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SimpleCarnivorousCreature_EW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Simple Carnivorous Creature</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Upon dealing damage or manually moving, deal 2 indirect damage to a random enemy. 
-This item will evolve after either dealing damage 3 times or manually moving 3 times.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>The mandibles are sharp, the brain is almost nonexistent.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SimpleHerbivoreCreature_EW</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Simple Herbivore Creature</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Upon receiving any damage or manually moving, heal 2 health to a random ally. 
-This item will evolve after either receiving any damage 3 times or manually moving 3 times.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>The heart full of peace, the brain is almost nonexistent.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NewlyFormedSpecies_TW</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Newly Formed Species</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>This item will evolve after either dealing damage 3 times or recieving any damage 3 times.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>The beggining of an amazing cosmic adventure.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MemoryRose_SW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Memory Rose</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>30% chance to refresh this party member's movement upon manually moving. The chance is increased by 5% per point of health missing (max 80% in total).</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>The wind on your skin. The pain in your heart.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>FailedMask_TW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Failed Mask</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>This party member starts combat with Spotlight. Other party members start combat with 5 Infirm.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>It wasn't perfect, but it showed who you really are.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>InhabitedHat_TW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Inhabited Hat</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Gain Focused on turn start. 
-Receive 1 indirect damage upon manually moving.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Those little friends inside my head.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ThornRing_TW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Thorn Ring</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>This item deals 1 damage to this party member at the beginning of each turn. 
-Adds the ability \</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Proceed.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CherishedLock_SW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cherished Lock</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Every third ability used by this party member grants ability and movement refresh.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>The wind is calling me...\</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>FearSense_TW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Fear Sense</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>At the end of each turh, inflict 2 Scars and 2 Infirm to each enemy at full health.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Know more about a monster's fear.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BoxingGloves_SW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Boxing Gloves</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>On combat start replace this party member's moveset with a strong offensive one with a rather high red pigment costs.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>It has always been my passion. Beating people, I mean.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SupremeCarnivorousCreature_EW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Supreme Carnivorous Creature</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Upon dealing damage deal 5 indirect damage to a random enemy 2 times.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>The jaw of incredible strength, the brain could develop a little more.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SupremeHerbivoreCreature_EW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supreme Herbivore Creature</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Upon receiving any damage heal 3 health to a random ally 2 times.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Flirtatiousness and Intelligence are off the charts.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SupremeOmnivoreCreature_EW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supreme Omnivore Creature</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Upon manually moving gain 4 Shield. 40% chance to also refresh movement</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Jack of all traits, master of none.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SimpleCarnivorousCreature_EW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Simple Carnivorous Creature</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Upon dealing damage or manually moving, deal 2 indirect damage to a random enemy. 
-This item will evolve after either dealing damage 3 times ot manually moving 3 times.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>The mandibles are sharp, the brain is almost nonexistent.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SimpleHerbivoreCreature_EW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Simple Herbivore Creature</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Upon receiving any damage or manually moving, heal 2 health to a random ally. 
-This item will evolve after either receiving any damage 3 times ot manually moving 3 times.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>The heart full of piece, the brain is almost nonexistent.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NewlyFormedSpecies_TW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Newly Formed Species</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>This item will evolve after either dealing damage 3 times ot recieving any damage 3 times.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>The beggining of an amazing cosmic adventure.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>QTips_SW</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Q-Tips</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Consume 1 Yellow pigment from the pigment bar at the end of each turn. If successful remove all status effects from this party member and heal them 2 health.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Clean the excess, feel better.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LocalLegalization_SW</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Local Legalization</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Start combat with all possible split pigment variations. 
-Receiving ANY damage destroys this item and consumes all pigment.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>A lot more pigment. No one will judge.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>EverlastingSentientGrinder_TW</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Everlasting Sentient Grinder</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>This party member now has Sparkling as a passive. 
-Adds \</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Guy so cool it hurts my eyes.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>GoldenLootbug_TW</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Golden Lootbug</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>At the end of combat pet the bug and maybe gain a coin. 
-Adds \</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>We're rich!\</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Incense_SW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Incense</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>On turn start and upon getting damaged increase lucky pigment chance by 10%.
-On turn end, if lucky pigment chance is at 100%, heal this party member by 4.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Smells funny.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>GinieLarva_TW</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Ginie Larva</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Heal 2 health upon receiving direct damage.
-30% chance to receive 1 indirect damage upon getting healed.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Immature, harmful, childish, malicious, but protection non the less.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>SeveredHeadsofMerchants_SW</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Severed Heads of Merchants</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>On combat end, produce a shop item. 
-Lose 2-4 coins upon receiving any damage. 10% chance to also destroy this item.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>They are putting a price on themselfs.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>GamblersHat_SW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Gambler's Hat</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>On combat start, receive 1 indirect damage and gain addictional random high-cost ability that produces money and gives various bonuses.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Looks like we found out who the real Joker is!\</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>EmergingFiends_TW</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Emerging Fiends</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>At the start of combat deal 2 direct damage to this party member and apply 1-2 Partaking to this party member.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>You meant \</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>RedFlag_TW</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Red Flag</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>At the start of combat give this party member an addictional ability that can heal party members and transfer to them.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Only one mouth to feed.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>HeadBurster_TW</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Head Burster</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Heal this party member 0 health each turn. Adds \</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Good day.\</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>LittleBallofHatred_TW</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Little Ball of Hatred</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Whenever enemy dies, inflict 2 Scars to All enemies and 1 Scar to this party member.</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>It stings and hisses. Such a rude thing.\</t>
+          <t>\!Let that sink in.\!</t>
         </is>
       </c>
     </row>

--- a/borchestra_items.xlsx
+++ b/borchestra_items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,682 +441,1260 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GF_Chalcanthite_OS</t>
+          <t>CalciumSupplement_SW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chalcanthite</t>
+          <t>Calcium Supplement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Upon lucky pigment being generated, apply triple the lucky pigment generated as Shield to this party member's slot.</t>
+          <t>This party member is now one level higher.
+This party member now has Inanimate as a passive.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>\!Vitriolic blues.\!</t>
+          <t>\!Bones like Titanium.\!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GF_Golden_Pickaxe_EW</t>
+          <t>TheInhumanSoul_TW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Golden Pickaxe</t>
+          <t>The Inhuman Soul</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>When this party member deals damage, 30% chance to gain 3 coins. 15% chance to consume this item when this effect triggers.</t>
+          <t>On combat start, give this party member a random ability of any other party member as an additional ability.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>\!Gold digging for dummies.\!</t>
+          <t>\!The missing screw.\!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GF_Candy_Stones_MA</t>
+          <t>ForeverAlone_TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Candy Stones</t>
+          <t>Forever Alone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>At the end of the turn, heal this party member 1 health and apply 2 Shield to their slot.</t>
+          <t>This party member deals, 2 more damage per empty slot in your party.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>\!Better than gelt!\!</t>
+          <t>\!Maybe it's better this way...\!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GF_Irish_Car_Bomb_OS</t>
+          <t>Guilt_TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Irish Car Bomb</t>
+          <t>Guilt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adds 'Drink Under' as an extra ability, a potent but dangerous damaging move that hits everyone.</t>
+          <t>Upon any party member performing an ability, very small chance to refresh this party member.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>\!What happens in...\!</t>
+          <t>\!The unseen organ.\!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GF_Off_Brandy_EW</t>
+          <t>WormyCrown_TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Off-Brandy</t>
+          <t>Wormy Crown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adds Tainted and Leaky to this party member as additional passives.</t>
+          <t>This party member now has Infestation (2) as a passive.
+On combat start spawn as many Festring Piles and Kekos as possible.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>\!Poor man's poison.\!</t>
+          <t>\!Lord of all things squirming.\!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GF_Whiskey_Stone_MA</t>
+          <t>GeneticInjection_TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Whiskey Stones</t>
+          <t>Genetic Injection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>This party member now has Grey health, along with the Inanimate and Swift Passives.</t>
+          <t>Gives this party member an additional ability \!Artificial Lycanthropy\! a chaotic maelstrom of enemy abilities.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>\!Whiskey, soured.\!</t>
+          <t>\!It's not supposed to grow those...\!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GF_Sergal_Spear_OS</t>
+          <t>SgilpsSkull_TW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sergal Spear</t>
+          <t>Sgilps' Skull</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>This party member does 2 additional damage with abilities, but exhausts their movement after using an ability.</t>
+          <t>The yellow pigment generator can now generate yellow pigment split with other random pigment.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>\!Requires two hands to wield.\!</t>
+          <t>\!Failed experiment.\!</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GF_Nap_Sack_OS</t>
+          <t>GlassTube_TW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nap Sack</t>
+          <t>Glass Tube</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>This unit is Exhausted at the start of the first turn. Apply 2 Well-Rested to this party member at the start of the first turn.</t>
+          <t>Prevent this party member's death, upon death kill a random other party member, and heal this party member for the amount of health they had.
+If there are no other party members do not prevent this party member's death.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>\!Get in the bag!\!</t>
+          <t>\!What yours is mine.\!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GF_Plastic_Bag_HV</t>
+          <t>PissOff_SW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plastic Bag</t>
+          <t>Piss Off</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>When this party member is manually swapped to a slot, 1 Constricted is applied to the Opposing slot.</t>
+          <t>Adds an ability \!F@#% This!\!, which allows party members to flee.... coward.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>\!Do you ever feel...\!</t>
+          <t>\!What you think you'd get something good?\!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GF_Crab_Claw_OS</t>
+          <t>CoinofAvarice_TW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crab Claw</t>
+          <t>Coin of Avarice</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>This party member has Constricting and Dominance as additional passives.</t>
+          <t>On combat start, deal 1 Indirect damage to all party members.
+50% chance to produce 20 coins. If unsuccessful, instantly kill this party member.
+Does not work on Nowak or Mung.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>\!What happens in...\!</t>
+          <t>\!There's no cheating this.\!</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GF_Inscissors_HV</t>
+          <t>BraggartsMouthpiece_TW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inscissors</t>
+          <t>Braggart’s Mouthpiece</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>When this party member uses an ability, deal 1 damage to them and then heal them 2 health.</t>
+          <t>Upon killing an enemy gain spotlight, and Move all enemies closer to this party member.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>\!Cut your teeth on it.\!</t>
+          <t>\!Toot your own horn.\!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GF_Neural_Worm_EW</t>
+          <t>FaultyMachineGun_SW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neural Worm</t>
+          <t>Faulty Machine Gun</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>This party member has a 40% chance to be Exhausted on turn start, and a 60% chance to perform a random ability.</t>
+          <t>Adds an extra ability to this party member \!Rattle\!, a strong attack that may produce a lot of pigment.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>\!Weak to fluoride.\!</t>
+          <t>\!The size of your gun doesn't matter.\!</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GF_Embalming_Fluid_MA</t>
+          <t>PotassiumNightcap_TW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Embalming Fluid</t>
+          <t>Potassium Nightcap</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Left and Right party members gain Immortal and are inflicted with 2 Scars at the start of combat.</t>
+          <t>At the start of every turn Transform this party member, into a random other party member of the same level.
+Maintain max health.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>\!Comfy company, a human quilt…\!</t>
+          <t>\!No banana make you go insane.\!</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GF_Naked_Knight_OS</t>
+          <t>VanishedKnight_TW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Little Knight</t>
+          <t>Vanished Knight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>When this party member uses an ability, a coinflip occurs. There is a 50% chance to apply 5 Shield to their position, and a 50% chance to deal 5 Damage to the Opposing enemy.</t>
+          <t>On combat start replace this party member's moveset with a generic offensive based one, that scales with level.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>\!He's pulling his sword out!\!</t>
+          <t>\!Don't be yourself.\!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GF_TowerShield_HV</t>
+          <t>FryingPan_SW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tower Shield</t>
+          <t>Frying Pan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>When this party member uses an ability, apply 3 Shield to the Left and Right allies.</t>
+          <t>Adds an additional ability to this party member \!Melee Swing\! a weak attack that has a chance to deal large damage.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>\!Tower defense.\!</t>
+          <t>\!Fair and Balanced.\!</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GF_Love_Letter_OS</t>
+          <t>CagedBeast_TW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Love Letter</t>
+          <t>Caged Beast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>At the start of combat, applies Gaze to the Opposing enemy. This party member deals 4 extra damage to Gazed enemies.</t>
+          <t>On combat start, spawn a clone of this party member. The clone has this party member's missing ability instead of Slap.
+This party member and the clone has 50% less max health than usual.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>\!Exodus 20:17\!</t>
+          <t>\!The Lizard Brain.\!</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GF_GlassEye_HV</t>
+          <t>Clonion_TW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Second Glass Eye</t>
+          <t>Clonion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>When using an ability, there is a 20% chance to cancel one of the Opposing enemy's abilities.</t>
+          <t>Upon killing an enemy, spawn a Mordrake clone.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>\!It gazes... intently.\!</t>
+          <t>\!Dandori.\!</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GF_Blessed_Goblet_EW</t>
+          <t>DecapitatedRooster_TW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Glistening Goblet</t>
+          <t>Decapitated Rooster</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>When using an ability, this party member heals for the current amount of overflow.</t>
+          <t>Upon killing an enemy, 50% chance to Refresh this party member's abilities and movement.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>\!Humbly, a toast.\!</t>
+          <t>\!I do enjoy hurting other people.\!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GF_Apache_Tears_MA</t>
+          <t>ArchaicMedicine_SW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apache Tears</t>
+          <t>Scalpel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>At the start of the turn, applies 5 Divine Protection to a random party member that doesn't have any. If all party members have Divine Protection, instead heal all party members 6 health and cleanse them of all status effects.</t>
+          <t>This party member's maximum health is decreased by 5 and deals 5 damage less than they would otherwise.
+This party member is 1 level higher than they would be otherwise.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>\!Unearthed by ApacheThunder!\!</t>
+          <t>\!You can call me doctor practice.\!</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GF_Panic_Button_OS</t>
+          <t>CandleffLife_TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Panic Button</t>
+          <t>Candle of Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Upon taking what would be lethal damage, this party member instead flees with one health. Ineffective on instant kills. Consumed on use.</t>
+          <t>This party member heals for 50% more than they otherwise would have.
+This party member has Dying as a passive.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>\!EMERGENCY!!!\!</t>
+          <t>\!Slow and insidious killer.\!</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GF_StickyNote_HV</t>
+          <t>LightSwitch_TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sticky Note</t>
+          <t>Light Switch</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>At the start of combat, the Left and Right party members have the costs of all their abilities removed.</t>
+          <t>On combat start, certain enemy types and factions will be swapped for an alternative but similar enemy faction.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>\!//TBD\!</t>
+          <t>\!1/64.\!</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GF_Dusty_Keyboard_MA</t>
+          <t>Transference_TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dusty Keyboard</t>
+          <t>Transference</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Before using an ability, a random status effect that this party member has is reduced by 2.</t>
+          <t>Gives this party member an additional ability that allows them to enter enemies.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>\!Still intact?\!</t>
+          <t>\!Ascension through sensation.\!</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GF_Liquid_Hate_OS</t>
+          <t>BrokenRecord_EW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liquid Hate</t>
+          <t>Broken Record</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>This party member does 3 additional damage with abilities, but all damage dealt to this party member penetrates Shield.</t>
+          <t>Adds an ability \!Same Routine\! a controllable(?) way to cancel enemy moves.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>\!This flesh, it hates.\!</t>
+          <t>\!It's getting old.\!</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GF_Rose_Tinted_Glasses_MA</t>
+          <t>AbstruseRelic_SW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rose-Tinted Glasses</t>
+          <t>Abstruse Relic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Adds 'Nostalgia' as an extra ability, an ability that performs a random party member's ability.</t>
+          <t>Adds an ability \!Record Scratch\! a controllable way to cancel enemy moves.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>\!It was better in the before-fore.\!</t>
+          <t>\!Fair and Balanced.\!</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GF_Heart_Of_Pyrite_OS</t>
+          <t>DiscardedCross_TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Heart of Pyrite</t>
+          <t>Discarded Cross</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Upon this party member taking damage, gain an equivelent amount of gold and consume this item.</t>
+          <t>Adds an additional ability to this party member \!Lenghty Excommunication\! a slow but powerful ability.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>\!Willing to trade it for worthless dollars.\!</t>
+          <t>\!So be it.\!</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GF_Amniotic_Fluids_HV</t>
+          <t>Person_EW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amniotic Fluids</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>When this party member takes damage, the Left or Right party member is healed 5 HP.</t>
+          <t>On combat start, produce 1 coin.
+10% chance to be consumed on use.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>\!Stop being a baby!\!</t>
+          <t>\!These are all over the place.\!</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GF_ManifestationOfWar_OS</t>
+          <t>CeramicArmor_EW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Manifestation Of War</t>
+          <t>Ceramic Armor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Upon an enemy dying, refresh this party member's abilities.</t>
+          <t>Lowers all direct damage taken by 3.
+5% chance to be consumed on use.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>\!Book of Revelations, chapter seven!\!</t>
+          <t>\!Like tapping on the side of a porcelain cup.\!</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GF_The_Tick_EW</t>
+          <t>BleedingEars_TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Tick</t>
+          <t>Bleeding Ears</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>At the start of combat, this party member's abilities are all changed to only cost Red.</t>
+          <t>This party member is now considered a \!Main Character\!.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>\!No, not that one.\!</t>
+          <t>\!Godly sigil.\!</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GF_Adverse_Action_Notice_OS</t>
+          <t>YourFault_TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adverse Action Notice</t>
+          <t>Your Fault</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>When this party member takes damage, this item has an 80% chance to negate it, and a 20% chance to multiply it by one to seven.</t>
+          <t>Upon this party member performing an ability, deal 2 indirect damage to them and increase their attack damage by 1.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>\!Begged them for repentance!\!</t>
+          <t>\!That is not the sun rising.\!</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GF_FaustianContract_HV</t>
+          <t>HappyPills_SW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Faustian Contract</t>
+          <t>Happy Pills</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>This party member gains Fatalism as a passive, protecting them from indirect and direct damage completely. After 3 turns, this party member is killed instantly.</t>
+          <t>Every even turn, this party member deals 3 more Damage, and heals 3 health.
+Every odd turn this party member deals 3 less damage.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>\!Stumblin’ on down my side of the road.\!</t>
+          <t>\!Down in your heart.\!</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GF_Cement_Shoes_MA</t>
+          <t>Vermin_TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cement Shoes</t>
+          <t>Vermin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Adds Anchored to this party member as an additional passive, but heals them 5 health at the end of every turn.</t>
+          <t>On combat start attempt to spawn an annoying Vermin on the enemy side, upon killing said Vermin heal all party members 3 Health.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>\!Let that sink in.\!</t>
+          <t>\!They hide poorly.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BloodyValve_SW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bloody Valve</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lose the ability to see Enemy and Party member health.
+Produce 3-4 \!Fish\! on combat end.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>\!This is a piece of garbage, and you're a piece of s&amp;%$.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DemonDagger_EW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Demon Dagger</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Decrease this Party member's Max Health by 75%. Increase all party member's damage by 4.
+Full Potential.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>\!DISCARNATED\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GoldDagger_EW</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gold Dagger</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Decrease this Party member's Max Health by 75%. Increase all party member's damage by 3.
+At the end of combat, Convert a future item into a better Dagger and consume this item.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>\!EVISCERATED\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SilverDagger_EW</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Silver Dagger</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Decrease this Party member's Max Health by 75%. Increase all party member's damage by 2.
+At the end of combat, Convert a future item into a better Dagger and consume this item.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>\!INTOXICATED\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CopperDagger_TW</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Copper Dagger</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Decrease this Party member's Max Health by 75%. Increase all party member's damage by 1.
+At the end of combat, Convert a future item into a better Dagger and consume this item.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>\!SWARMED\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chloroform_EW</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chloroform</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>On combat start, deal 3 Indirect damage to all enemies.
+Inflict 0-1 fire on each enemy position.
+Destroy this item upon use.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>\!Napsack.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GasGrenade_EW</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gas Grenade</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>On combat start, deal 6 Indirect damage to all enemies.
+Inflict 0-3 fire on each enemy position.
+Destroy this item upon use.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>\!A sober person would throw it.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DeadCanary_SW</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Dead Canary</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>On combat start, increase the health of bosses by 25%.
+Upon defeating the boss, gain a number of unique helpful items..</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>\!Miserable.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BurntLetter_SW</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Burnt Letter</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>This party member now deals half their Direct damage as Fire damage.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>\!Just for me-e-e.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LooseScarf_SW</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Loose Scarf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>This party member can move twice per turn.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>\!Friends made along the way.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sugar_SW</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>If this party member received damage, heal this party member 1-3 Health at the end of the turn.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>\!The most important element.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TaliasSeveredHead_TW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Talia's Severed Head</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Heal this party member 3 health at the end of each turn.
+Upon taking any kind of damage, grant alien information.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>\!Like God, but less impressive.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SkeletonBanana_EW</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Skeleton Banana</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Upon moving this party member apply 1 Constricting to the opposing position.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>\!I don't think that;s how it works.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GizoEgg_EW</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gizo Egg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Upon moving this party member apply 1 Constricting to the opposing position.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>\!You can make a really terrible omelette with this.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EctoplasmicEmesis_EW</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ectoplasmic Emesis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>50% chance Heal this party member 2 Health at the end of each turn, if this doesn't heal instead produce 1 Purple/Blue split pigment.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>\!Barely even there.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BronzeDroplet_EW</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bronze Droplet</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spawn a Copper Cougher on combat start.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>\!Pathetic.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AdorableTeacup_EW</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Adorable Teacup</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>This party member can move twice per turn.
+This party member now has Slippery and Skittish as passives.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>\!Aw how heartburning.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SweatyCloth_EW</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sweaty Cloth</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>This party member now has 70% less Maximum health.
+This party member now has Classic as a passive.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>\!Look at you go!\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BoneHalo_EW</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bone Halo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>his party member now Inferno, Blazing and Immortal as passives.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>\!These are NOT angels...\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TheEnemyPack_TW</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The Enemy Pack</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>On combat start produce several helpful items and consume this item.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>\!Who made this sh$%!?\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RubberGloves_SW</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rubber Gloves</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Upon this party member performing Slap, refresh their movement and abilities.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>\!The crunchiest slap there is.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CoinGun_SW</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Coin Gun</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Add an extra ability to this party member, \!Coin gun\!, a powerful endlessly repeatable attack that drains you of money.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>\!Videogame cliche.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RadiationJar_SW</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Radiation Jar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Apply permanent Gutted to this party member at the start of Combat.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>\!I hope you weren't carrying this around in your pocket.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SnakeOil_SW</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Snake Oil</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>70% chance to lose 1 coin at the start of each turn.
+Gain 2x more money at the end of combat.
+20% chance to be destroyed at the end of combat.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>\!A hundred percent proven to cure the cold. And rabies. And cancer. Also makes you immortal.\!</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EffigyofaBastard_TW</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Effigy of a Bastard</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>This party member now deals 15% more damage to enemies.
+This party member now deals 100% more damage if the attacked enemy is an amphibian.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>\!Never again...\!</t>
         </is>
       </c>
     </row>
